--- a/Circuit Examples/Folded Cascode OTA/Folded_cascode_OTA_v1.xlsx
+++ b/Circuit Examples/Folded Cascode OTA/Folded_cascode_OTA_v1.xlsx
@@ -555,7 +555,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.55</v>
+        <v>0.53</v>
       </c>
     </row>
     <row r="6">
@@ -565,7 +565,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.45</v>
+        <v>0.58</v>
       </c>
     </row>
   </sheetData>
